--- a/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,29; 57,71</t>
+          <t>36,58; 56,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,53; 47,46</t>
+          <t>24,14; 45,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 45,75</t>
+          <t>18,52; 42,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,4; 59,87</t>
+          <t>38,28; 60,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,28; 55,72</t>
+          <t>35,7; 56,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 35,34</t>
+          <t>15,05; 35,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,45; 55,22</t>
+          <t>40,49; 54,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,47; 48,81</t>
+          <t>34,03; 48,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,9; 34,95</t>
+          <t>19,7; 35,62</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,52; 50,57</t>
+          <t>31,94; 50,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 30,44</t>
+          <t>13,4; 29,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,74; 35,0</t>
+          <t>14,16; 35,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,43; 64,68</t>
+          <t>45,4; 65,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 45,81</t>
+          <t>28,9; 45,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,98; 54,94</t>
+          <t>27,65; 54,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,55; 55,67</t>
+          <t>41,45; 55,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,73; 35,12</t>
+          <t>23,95; 36,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,45; 42,1</t>
+          <t>24,19; 42,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,56; 46,35</t>
+          <t>27,2; 46,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,91; 45,61</t>
+          <t>21,07; 43,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 43,29</t>
+          <t>9,15; 43,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,06; 69,45</t>
+          <t>49,52; 69,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,88; 58,03</t>
+          <t>35,49; 57,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 60,6</t>
+          <t>27,83; 60,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 54,01</t>
+          <t>40,47; 55,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,79; 47,35</t>
+          <t>32,17; 47,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,32; 51,62</t>
+          <t>23,78; 49,72</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,51; 53,99</t>
+          <t>39,74; 53,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 46,91</t>
+          <t>33,41; 46,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 38,83</t>
+          <t>11,19; 38,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,58; 61,79</t>
+          <t>49,34; 62,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,87; 51,33</t>
+          <t>37,33; 51,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 56,92</t>
+          <t>33,82; 56,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,86; 57,09</t>
+          <t>46,9; 56,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,56; 46,97</t>
+          <t>37,36; 46,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 44,0</t>
+          <t>21,7; 43,94</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,59; 57,61</t>
+          <t>41,68; 57,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,36; 44,74</t>
+          <t>28,33; 43,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,64; 65,87</t>
+          <t>34,67; 65,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,45; 56,76</t>
+          <t>40,9; 57,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,28; 56,47</t>
+          <t>39,88; 56,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,74; 59,21</t>
+          <t>36,32; 58,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,66; 55,41</t>
+          <t>43,57; 55,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,98; 47,53</t>
+          <t>36,48; 48,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,23; 58,12</t>
+          <t>39,58; 58,18</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,63; 63,7</t>
+          <t>37,51; 63,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,66; 52,26</t>
+          <t>27,38; 52,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 32,38</t>
+          <t>4,65; 29,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,4; 65,17</t>
+          <t>43,06; 64,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,62; 61,46</t>
+          <t>36,1; 59,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,31; 59,61</t>
+          <t>26,8; 58,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,3; 61,73</t>
+          <t>43,95; 61,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,92; 53,39</t>
+          <t>35,65; 53,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,06; 42,73</t>
+          <t>20,7; 41,54</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,84; 49,62</t>
+          <t>41,8; 49,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,13; 38,37</t>
+          <t>30,76; 38,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,34; 33,91</t>
+          <t>19,5; 34,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,96; 57,8</t>
+          <t>50,47; 57,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,07; 48,58</t>
+          <t>41,27; 48,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,23; 46,05</t>
+          <t>35,45; 46,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,38; 52,65</t>
+          <t>47,04; 52,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,41; 42,37</t>
+          <t>37,48; 42,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,14; 39,02</t>
+          <t>29,81; 39,23</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>31300</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11757</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28461</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30054</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13825</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59760</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>48797</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24401; 37576</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12839; 24363</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7239; 16709</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22007; 34976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23127; 36670</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8398; 19997</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50283; 68004</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>40145; 57195</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18697; 33794</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>28624</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14270</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9002</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38393</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30585</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17883</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67017</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>44855</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26885</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22500; 35573</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9360; 20657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5582; 14077</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31185; 44979</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23864; 37882</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11877; 23581</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>57670; 77007</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>36504; 55080</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>19927; 35331</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36156</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14345</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58360</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>40745</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18042</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16828; 29015</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9638; 19757</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1544; 7270</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30271; 42240</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20290; 32873</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9010; 19711</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>49782; 67910</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>33113; 48759</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11714; 24490</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>61694</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60341</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26777</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86819</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64320</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38328</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>148514</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>124661</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>65105</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>52346; 70726</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50346; 69797</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11605; 40424</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>76705; 96990</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>54016; 74425</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>29087; 48475</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>134686; 161827</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>110361; 137763</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>41163; 83355</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>54416</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18177</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>48443</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48167</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26955</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>102859</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>83193</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>45132</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>45234; 62794</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27592; 42704</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12699; 24161</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40354; 56273</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>40314; 56770</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20738; 33647</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>90266; 114573</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>72393; 95708</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>37101; 54533</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>20876</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17233</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3649</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>29305</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>24577</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>15340</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>50181</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>41810</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>18989</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>15369; 26175</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11975; 23021</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1203; 7521</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23278; 34923</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>18160; 29855</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9715; 21044</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>41765; 58140</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>33530; 50374</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>12859; 25800</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>219114</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159750</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>73058</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>267577</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>224310</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>126677</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>486691</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>384060</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>199735</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>200746; 235931</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>141700; 177234</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>51022; 89179</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>250051; 286166</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>206595; 242361</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>110048; 143570</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>459015; 510764</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>360278; 409862</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>170514; 224411</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,58; 56,34</t>
+          <t>36,19; 56,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,14; 45,8</t>
+          <t>25,23; 46,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 42,74</t>
+          <t>18,48; 42,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,28; 60,84</t>
+          <t>38,7; 59,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,7; 56,61</t>
+          <t>36,32; 55,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 35,84</t>
+          <t>15,17; 36,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,49; 54,76</t>
+          <t>39,99; 55,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,03; 48,48</t>
+          <t>34,56; 49,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 35,62</t>
+          <t>19,74; 36,08</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,94; 50,5</t>
+          <t>30,93; 50,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 29,57</t>
+          <t>13,31; 29,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 35,7</t>
+          <t>13,66; 34,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,4; 65,49</t>
+          <t>46,31; 66,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,9; 45,88</t>
+          <t>28,14; 45,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,65; 54,9</t>
+          <t>27,9; 55,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,45; 55,35</t>
+          <t>41,23; 55,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 36,13</t>
+          <t>22,95; 34,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,19; 42,89</t>
+          <t>24,4; 41,82</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,2; 46,9</t>
+          <t>27,4; 47,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,07; 43,18</t>
+          <t>20,38; 42,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 43,07</t>
+          <t>9,41; 42,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 69,1</t>
+          <t>49,36; 69,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,49; 57,49</t>
+          <t>36,34; 57,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,83; 60,89</t>
+          <t>28,26; 61,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,47; 55,21</t>
+          <t>40,12; 54,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,17; 47,37</t>
+          <t>32,23; 48,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,78; 49,72</t>
+          <t>24,32; 49,55</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,74; 53,69</t>
+          <t>39,55; 53,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,41; 46,32</t>
+          <t>33,76; 47,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 38,98</t>
+          <t>9,98; 38,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,34; 62,39</t>
+          <t>49,06; 62,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,33; 51,43</t>
+          <t>38,26; 51,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,82; 56,36</t>
+          <t>34,12; 56,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,9; 56,35</t>
+          <t>46,68; 56,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,36; 46,64</t>
+          <t>37,77; 47,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 43,94</t>
+          <t>20,69; 43,46</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,68; 57,87</t>
+          <t>41,68; 57,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,33; 43,85</t>
+          <t>27,96; 43,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,67; 65,96</t>
+          <t>35,13; 65,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,9; 57,04</t>
+          <t>41,28; 57,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,88; 56,16</t>
+          <t>37,86; 54,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,32; 58,93</t>
+          <t>35,22; 59,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,57; 55,3</t>
+          <t>43,93; 55,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,48; 48,22</t>
+          <t>35,75; 48,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,58; 58,18</t>
+          <t>39,78; 57,06</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,51; 63,88</t>
+          <t>38,24; 65,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,38; 52,63</t>
+          <t>27,7; 52,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 29,09</t>
+          <t>4,46; 31,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,06; 64,6</t>
+          <t>42,62; 65,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,1; 59,35</t>
+          <t>37,98; 61,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,8; 58,05</t>
+          <t>28,25; 58,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,95; 61,18</t>
+          <t>44,43; 61,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,65; 53,56</t>
+          <t>36,15; 53,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,7; 41,54</t>
+          <t>20,23; 41,62</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,8; 49,13</t>
+          <t>42,01; 49,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,76; 38,48</t>
+          <t>31,37; 38,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,09</t>
+          <t>19,13; 34,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,47; 57,76</t>
+          <t>50,14; 57,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,27; 48,41</t>
+          <t>40,81; 48,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,45; 46,24</t>
+          <t>35,81; 46,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,04; 52,35</t>
+          <t>47,14; 52,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,48; 42,64</t>
+          <t>37,24; 42,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,81; 39,23</t>
+          <t>29,92; 39,52</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24401; 37576</t>
+          <t>24138; 37980</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12839; 24363</t>
+          <t>13422; 24719</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7239; 16709</t>
+          <t>7224; 16546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22007; 34976</t>
+          <t>22248; 34270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23127; 36670</t>
+          <t>23530; 36225</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8398; 19997</t>
+          <t>8466; 20294</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50283; 68004</t>
+          <t>49658; 68764</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40145; 57195</t>
+          <t>40763; 58451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18697; 33794</t>
+          <t>18732; 34234</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22500; 35573</t>
+          <t>21786; 35484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9360; 20657</t>
+          <t>9301; 20644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5582; 14077</t>
+          <t>5385; 13781</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31185; 44979</t>
+          <t>31807; 45395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23864; 37882</t>
+          <t>23236; 37618</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11877; 23581</t>
+          <t>11985; 23651</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57670; 77007</t>
+          <t>57361; 76770</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36504; 55080</t>
+          <t>34978; 52975</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19927; 35331</t>
+          <t>20099; 34452</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16828; 29015</t>
+          <t>16951; 29245</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9638; 19757</t>
+          <t>9323; 19278</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1544; 7270</t>
+          <t>1588; 7095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30271; 42240</t>
+          <t>30170; 42272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20290; 32873</t>
+          <t>20778; 32838</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9010; 19711</t>
+          <t>9148; 19926</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49782; 67910</t>
+          <t>49346; 67313</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33113; 48759</t>
+          <t>33170; 49645</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11714; 24490</t>
+          <t>11978; 24406</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52346; 70726</t>
+          <t>52102; 71083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50346; 69797</t>
+          <t>50875; 72290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11605; 40424</t>
+          <t>10347; 40162</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76705; 96990</t>
+          <t>76271; 96675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54016; 74425</t>
+          <t>55370; 74701</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29087; 48475</t>
+          <t>29346; 48723</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134686; 161827</t>
+          <t>134061; 162321</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110361; 137763</t>
+          <t>111562; 139284</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41163; 83355</t>
+          <t>39250; 82452</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45234; 62794</t>
+          <t>45229; 62295</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27592; 42704</t>
+          <t>27234; 42067</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12699; 24161</t>
+          <t>12869; 24057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40354; 56273</t>
+          <t>40727; 56711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40314; 56770</t>
+          <t>38272; 55522</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20738; 33647</t>
+          <t>20113; 33762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90266; 114573</t>
+          <t>91009; 114248</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72393; 95708</t>
+          <t>70959; 95337</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37101; 54533</t>
+          <t>37280; 53484</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15369; 26175</t>
+          <t>15667; 26813</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11975; 23021</t>
+          <t>12115; 22982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1203; 7521</t>
+          <t>1154; 8076</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23278; 34923</t>
+          <t>23039; 35164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18160; 29855</t>
+          <t>19107; 30811</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9715; 21044</t>
+          <t>10239; 21051</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41765; 58140</t>
+          <t>42223; 58320</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33530; 50374</t>
+          <t>34002; 49884</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12859; 25800</t>
+          <t>12564; 25853</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>200746; 235931</t>
+          <t>201756; 240072</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>141700; 177234</t>
+          <t>144494; 177050</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51022; 89179</t>
+          <t>50036; 89686</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250051; 286166</t>
+          <t>248434; 285340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>206595; 242361</t>
+          <t>204288; 242568</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>110048; 143570</t>
+          <t>111170; 143248</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>459015; 510764</t>
+          <t>459993; 510591</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>360278; 409862</t>
+          <t>357997; 408897</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170514; 224411</t>
+          <t>171194; 226084</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>46,93%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 56,94</t>
+          <t>38,4; 59,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,23; 46,47</t>
+          <t>36,28; 55,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 42,32</t>
+          <t>14,5; 35,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 59,61</t>
+          <t>37,29; 57,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,32; 55,92</t>
+          <t>24,53; 47,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 36,37</t>
+          <t>19,49; 45,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,99; 55,37</t>
+          <t>40,45; 55,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,56; 49,55</t>
+          <t>34,47; 48,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,74; 36,08</t>
+          <t>19,9; 35,43</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>40,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>20,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 50,37</t>
+          <t>45,43; 64,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 29,55</t>
+          <t>29,02; 45,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 34,95</t>
+          <t>28,71; 56,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,31; 66,09</t>
+          <t>31,52; 50,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,14; 45,56</t>
+          <t>14,05; 30,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,9; 55,06</t>
+          <t>13,38; 34,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,23; 55,18</t>
+          <t>41,55; 55,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,95; 34,75</t>
+          <t>23,73; 35,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,4; 41,82</t>
+          <t>24,69; 42,5</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46,32%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>35,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>30,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,4; 47,27</t>
+          <t>49,06; 69,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 42,14</t>
+          <t>35,88; 58,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 42,03</t>
+          <t>31,21; 62,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,36; 69,16</t>
+          <t>26,56; 46,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,34; 57,43</t>
+          <t>20,91; 45,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 61,55</t>
+          <t>9,71; 45,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,12; 54,73</t>
+          <t>39,5; 54,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,23; 48,23</t>
+          <t>31,79; 47,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,32; 49,55</t>
+          <t>26,53; 51,85</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>46,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>40,04%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,45%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,55; 53,96</t>
+          <t>48,58; 61,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,76; 47,97</t>
+          <t>37,87; 51,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 38,72</t>
+          <t>32,76; 55,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,06; 62,19</t>
+          <t>39,51; 53,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,26; 51,62</t>
+          <t>33,53; 46,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,12; 56,65</t>
+          <t>20,44; 37,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,68; 56,52</t>
+          <t>46,86; 57,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,77; 47,15</t>
+          <t>37,56; 46,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 43,46</t>
+          <t>28,86; 43,45</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46,69%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>50,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>35,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49,63%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,65%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,68; 57,41</t>
+          <t>40,45; 56,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,96; 43,19</t>
+          <t>39,28; 56,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,13; 65,68</t>
+          <t>36,08; 58,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,28; 57,48</t>
+          <t>42,59; 57,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,86; 54,93</t>
+          <t>28,36; 44,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,22; 59,13</t>
+          <t>34,09; 60,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,93; 55,15</t>
+          <t>43,66; 55,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,75; 48,04</t>
+          <t>35,98; 47,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,78; 57,06</t>
+          <t>37,92; 55,8</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54,21%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44,63%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>50,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>39,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54,21%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,24; 65,44</t>
+          <t>43,4; 65,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,7; 52,54</t>
+          <t>36,62; 61,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 31,23</t>
+          <t>29,27; 61,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,62; 65,05</t>
+          <t>37,63; 63,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,98; 61,25</t>
+          <t>27,66; 52,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,25; 58,07</t>
+          <t>5,42; 30,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,43; 61,37</t>
+          <t>44,3; 61,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,15; 53,04</t>
+          <t>36,92; 53,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,23; 41,62</t>
+          <t>20,88; 42,96</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44,81%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40,82%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>45,63%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>34,68%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>54,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,01; 49,99</t>
+          <t>49,96; 57,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,37; 38,44</t>
+          <t>41,07; 48,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,13; 34,28</t>
+          <t>35,28; 46,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,14; 57,59</t>
+          <t>41,84; 49,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,81; 48,45</t>
+          <t>31,13; 38,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,81; 46,14</t>
+          <t>23,02; 32,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,14; 52,33</t>
+          <t>47,38; 52,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,24; 42,54</t>
+          <t>37,41; 42,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,92; 39,52</t>
+          <t>31,63; 39,39</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28461</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30054</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13090</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>31300</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>18743</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11757</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28461</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30054</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>25159</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24138; 37980</t>
+          <t>22077; 34417</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13422; 24719</t>
+          <t>23502; 36097</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7224; 16546</t>
+          <t>7736; 18943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22248; 34270</t>
+          <t>24872; 38493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23530; 36225</t>
+          <t>13050; 25244</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8466; 20294</t>
+          <t>7734; 18205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49658; 68764</t>
+          <t>50229; 68574</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40763; 58451</t>
+          <t>40660; 57578</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18732; 34234</t>
+          <t>18514; 32966</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>38393</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30585</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17853</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>28624</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14270</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9002</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38393</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30585</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>26900</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21786; 35484</t>
+          <t>31199; 44422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9301; 20644</t>
+          <t>23957; 37826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5385; 13781</t>
+          <t>11975; 23419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31807; 45395</t>
+          <t>22205; 35624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23236; 37618</t>
+          <t>9818; 21265</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11985; 23651</t>
+          <t>5354; 13860</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57361; 76770</t>
+          <t>57802; 77455</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34978; 52975</t>
+          <t>36175; 53530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20099; 34452</t>
+          <t>20177; 34728</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>22205</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>14138</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3697</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36156</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26607</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>16762</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16951; 29245</t>
+          <t>29985; 42453</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9323; 19278</t>
+          <t>20514; 33181</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1588; 7095</t>
+          <t>8649; 17291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30170; 42272</t>
+          <t>16430; 28678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20778; 32838</t>
+          <t>9565; 20866</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9148; 19926</t>
+          <t>1658; 7700</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49346; 67313</t>
+          <t>48586; 66433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33170; 49645</t>
+          <t>32718; 48735</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11978; 24406</t>
+          <t>11879; 23218</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86819</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>64320</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34512</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>61694</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>60341</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26777</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86819</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64320</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38328</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65105</t>
+          <t>55635</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52102; 71083</t>
+          <t>75516; 96065</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50875; 72290</t>
+          <t>54796; 74281</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10347; 40162</t>
+          <t>26165; 44450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76271; 96675</t>
+          <t>52044; 71118</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55370; 74701</t>
+          <t>50523; 70684</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29346; 48723</t>
+          <t>15301; 27853</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134061; 162321</t>
+          <t>134576; 163946</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111562; 139284</t>
+          <t>110936; 138748</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39250; 82452</t>
+          <t>44659; 67226</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>48443</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48167</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24826</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>54416</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>35026</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18177</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>48443</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48167</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>40735</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45229; 62295</t>
+          <t>39910; 56002</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27234; 42067</t>
+          <t>39704; 57079</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12869; 24057</t>
+          <t>19181; 30935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40727; 56711</t>
+          <t>46215; 62518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38272; 55522</t>
+          <t>27615; 43567</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20113; 33762</t>
+          <t>11645; 20775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91009; 114248</t>
+          <t>90444; 114791</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>70959; 95337</t>
+          <t>71411; 94328</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37280; 53484</t>
+          <t>33119; 48728</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29305</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24577</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15194</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>20876</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>17233</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3649</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>29305</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>24577</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>18799</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15667; 26813</t>
+          <t>23459; 35227</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12115; 22982</t>
+          <t>18422; 30918</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1154; 8076</t>
+          <t>9965; 20854</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23039; 35164</t>
+          <t>15419; 26102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19107; 30811</t>
+          <t>12099; 22860</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10239; 21051</t>
+          <t>1473; 8309</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42223; 58320</t>
+          <t>42101; 58660</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34002; 49884</t>
+          <t>34727; 50211</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12564; 25853</t>
+          <t>12786; 26299</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>267577</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>224310</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>118309</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>219114</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>159750</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>73058</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>267577</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>224310</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>126677</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>199735</t>
+          <t>183988</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>201756; 240072</t>
+          <t>247548; 286405</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>144494; 177050</t>
+          <t>205594; 243178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50036; 89686</t>
+          <t>102253; 133619</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>248434; 285340</t>
+          <t>200931; 238290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>204288; 242568</t>
+          <t>143382; 176748</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>111170; 143248</t>
+          <t>53618; 76793</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>459993; 510591</t>
+          <t>462280; 513733</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>357997; 408897</t>
+          <t>359557; 407260</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>171194; 226084</t>
+          <t>165391; 205961</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Clase-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.4950883864855047</v>
+        <v>0.4721442466185505</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.4639644431789868</v>
+        <v>0.4304205301952377</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.2453074725274109</v>
+        <v>0.2601939043262253</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.4692583864642175</v>
+        <v>0.4580346939598904</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.3523770343304312</v>
+        <v>0.353590731538705</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.3040719973745114</v>
+        <v>0.2975963636105182</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.4812151082347214</v>
+        <v>0.4647509134375324</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.4136515777078792</v>
+        <v>0.3964094388068007</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.2703736689877505</v>
+        <v>0.2759150132596055</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3840372459698021</v>
+        <v>0.3752321057202086</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.3628175528688306</v>
+        <v>0.3395842972910213</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.1449736602885894</v>
+        <v>0.1628013394600248</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.3728916188208078</v>
+        <v>0.3611300007582769</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.2453493091855998</v>
+        <v>0.2733175632059021</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.1948606299224274</v>
+        <v>0.1836762250542637</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.4044630058641907</v>
+        <v>0.3912829008832519</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.3446736677530739</v>
+        <v>0.3326990214290708</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.1989621966833351</v>
+        <v>0.20313713730636</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.5986968559606604</v>
+        <v>0.5722619446107592</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.5572461660287884</v>
+        <v>0.5178657618593735</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.3550101786153673</v>
+        <v>0.376780566758476</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5771130529083938</v>
+        <v>0.5499100803891388</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.4746060265813586</v>
+        <v>0.4613178463794927</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.4586747190938486</v>
+        <v>0.4371136232166608</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5521902307891661</v>
+        <v>0.5322049200443035</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.4880898067108342</v>
+        <v>0.4621082008649425</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.3542774033438456</v>
+        <v>0.3544961867796946</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5590002895867078</v>
+        <v>0.559713150199066</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.3704225963839458</v>
+        <v>0.3848055374642713</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.4279946886298591</v>
+        <v>0.4215147042495658</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.4063203622065644</v>
+        <v>0.388490330729886</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2042574839303282</v>
+        <v>0.2045038615577777</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.2261622792098627</v>
+        <v>0.2114367487059814</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.4816927292635299</v>
+        <v>0.4755668064193305</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.2942645838876849</v>
+        <v>0.3006524073840594</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.3291913144812575</v>
+        <v>0.3159404689891355</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.4542515763993341</v>
+        <v>0.4706249711559162</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.2901527784880316</v>
+        <v>0.3059264484731631</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2870792971612113</v>
+        <v>0.2830651067350457</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3152085634980769</v>
+        <v>0.2987225942948434</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1405360730381515</v>
+        <v>0.1467104030108419</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.1338349014798279</v>
+        <v>0.1251979111660162</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4154595807116137</v>
+        <v>0.4082797513737278</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.2373247317076111</v>
+        <v>0.2471612028863786</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.2469254781142139</v>
+        <v>0.2369526875369</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.6467798255305163</v>
+        <v>0.654336960608853</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.4581193354382067</v>
+        <v>0.4617275054457644</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.561439150312588</v>
+        <v>0.5625503182566621</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.5056930415128734</v>
+        <v>0.4811557777313733</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.3043848704956998</v>
+        <v>0.2828191784241611</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3464868863215999</v>
+        <v>0.3321608056964345</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5567191840883861</v>
+        <v>0.5365198670338697</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.3511766592815423</v>
+        <v>0.3582487205889957</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.4249957781046009</v>
+        <v>0.4145942944219099</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.591495579012427</v>
+        <v>0.5745725708843314</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.4653391616987546</v>
+        <v>0.4837770867891391</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.4631545786922261</v>
+        <v>0.4376798603237079</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3589053252073557</v>
+        <v>0.3646165500836996</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.3090309998018835</v>
+        <v>0.303439267428426</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.2300828967869636</v>
+        <v>0.2459987332216569</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.4744978398139253</v>
+        <v>0.4665027776945819</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.3958627426121197</v>
+        <v>0.4026260834607225</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.3743162207524371</v>
+        <v>0.361072812573408</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4905506469355158</v>
+        <v>0.4763468436957478</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.3587806094213637</v>
+        <v>0.3825968564232778</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3121131133812513</v>
+        <v>0.2928628716238596</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.2655544860159486</v>
+        <v>0.2706607682690913</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2090622177653788</v>
+        <v>0.2115312234679032</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.09712291400918706</v>
+        <v>0.1151717948020793</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.3950298096731698</v>
+        <v>0.4002760498018049</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.3178724256526423</v>
+        <v>0.3371147219032791</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.2652872950474532</v>
+        <v>0.2572728656021662</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.6945190363597491</v>
+        <v>0.6720346684323676</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.5803050449002165</v>
+        <v>0.5748328126035832</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.6239847784174877</v>
+        <v>0.6075339020399102</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.4635310102916321</v>
+        <v>0.4562786053170155</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4560854585002428</v>
+        <v>0.4120143514358514</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.4511487328328252</v>
+        <v>0.4364910881804661</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.5401291793147451</v>
+        <v>0.5390668244659984</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.4734815222733221</v>
+        <v>0.4724594939405639</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.5185043300132467</v>
+        <v>0.4899271227258086</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5584697718743773</v>
+        <v>0.5310714897629524</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.4444876983695238</v>
+        <v>0.4631839175595278</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.4320796174583575</v>
+        <v>0.4343958513270552</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.4683187646268753</v>
+        <v>0.444433848002695</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.4004334649311307</v>
+        <v>0.3817540551331107</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.2821802332829729</v>
+        <v>0.2854064585885532</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.5171176456495484</v>
+        <v>0.4906586134886743</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.4220144563765982</v>
+        <v>0.4226575232880182</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.3595605918357767</v>
+        <v>0.3634770817561652</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.4857615266263439</v>
+        <v>0.4691529731954391</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.3786733518658981</v>
+        <v>0.4050025970356094</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.3275827814169261</v>
+        <v>0.32664695444081</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3950661475911985</v>
+        <v>0.3840466812610643</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.3352785339405721</v>
+        <v>0.3229425256679995</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.2044035554264337</v>
+        <v>0.2070222714906544</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.4685868099388488</v>
+        <v>0.4493455801527377</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.3755504989645277</v>
+        <v>0.3780404565361764</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.2886232154613662</v>
+        <v>0.3015514534420772</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.6179429993849284</v>
+        <v>0.5935359584627349</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.5133238128750438</v>
+        <v>0.5225932511533984</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.5565059936902863</v>
+        <v>0.5459380059827279</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.5398533414515673</v>
+        <v>0.5057628501249412</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.4690746645258742</v>
+        <v>0.4401437628459973</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.3720904634689053</v>
+        <v>0.3791765803161776</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5708511206834946</v>
+        <v>0.5365844204899429</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.469702838089411</v>
+        <v>0.4688451983202978</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.4344748816158981</v>
+        <v>0.4459530920797139</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.4910130155199303</v>
+        <v>0.4826667076753454</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.4765048001115075</v>
+        <v>0.4378340109592818</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.4669439987729551</v>
+        <v>0.4649596684071307</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.5014592777442417</v>
+        <v>0.5197316425220008</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.3596532192327975</v>
+        <v>0.3651431337152672</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.4656997393117255</v>
+        <v>0.5101755015521316</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.4964846494584426</v>
+        <v>0.5016787977957564</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.419166701450722</v>
+        <v>0.4020109509193902</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.4664572925398638</v>
+        <v>0.482948875218793</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.4045274292161258</v>
+        <v>0.41105587790296</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.3927831132638092</v>
+        <v>0.3650877346221329</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3607651473145992</v>
+        <v>0.3520446061602461</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.4258892205550592</v>
+        <v>0.4456767616719172</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.2835504861778964</v>
+        <v>0.2926832046843554</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.3409191867544041</v>
+        <v>0.3728904041898268</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.436558792902818</v>
+        <v>0.4483486864315634</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.359801715452724</v>
+        <v>0.3489380175803993</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3792477430009398</v>
+        <v>0.3951691586050876</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5676270840803367</v>
+        <v>0.5635023269474246</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.5646684471660797</v>
+        <v>0.5155951061446589</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.5818362417338362</v>
+        <v>0.5851856702461377</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5761201633934706</v>
+        <v>0.5931428118172647</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.4473522039700121</v>
+        <v>0.4415047820917247</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.6081889663860621</v>
+        <v>0.6337528628089223</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.5540801786217485</v>
+        <v>0.5502900229502886</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.4752696819868266</v>
+        <v>0.4565807861168629</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.5579891800564738</v>
+        <v>0.5692781317268175</v>
       </c>
     </row>
     <row r="19">
@@ -1177,28 +1177,28 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.5421267841278568</v>
+        <v>0.5347298651216033</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.488540548106995</v>
+        <v>0.4819565507956208</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0.4463492813907681</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.5094849537715198</v>
+        <v>0.535774939050665</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.3939503461214214</v>
+        <v>0.3675177166003735</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.1326384970240113</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.5280526257689994</v>
+        <v>0.5351661777304914</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.4445459004366074</v>
+        <v>0.4299168654940712</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0.3070645144564195</v>
@@ -1212,28 +1212,28 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.433976573721105</v>
+        <v>0.4257251139973388</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.3661925979531799</v>
+        <v>0.3787798351419578</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0.2927443415522034</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3763004831438864</v>
+        <v>0.4036308893530841</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.276600615386649</v>
+        <v>0.2668499346554004</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.05418147081599323</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.4430266725256092</v>
+        <v>0.462089231767097</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.3692421507988616</v>
+        <v>0.3502414052974245</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0.2088441516937503</v>
@@ -1247,28 +1247,28 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.6516770726052458</v>
+        <v>0.6355317523540791</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.6145893210880495</v>
+        <v>0.5909578056093808</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0.6126348813330529</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.6370391861613081</v>
+        <v>0.6595905664495053</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.5225964454344277</v>
+        <v>0.4902539443870248</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.3056888070120936</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.6172751970647706</v>
+        <v>0.6144928095158084</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.5338791474816577</v>
+        <v>0.5119929718795039</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0.4295681559085975</v>
@@ -1286,31 +1286,31 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.5400487697576704</v>
+        <v>0.5233098709991656</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.4480654188894941</v>
+        <v>0.4453687980742428</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.4081513143855126</v>
+        <v>0.4080958190249358</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.4562600371017859</v>
+        <v>0.4530573722418574</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.3468140949919547</v>
+        <v>0.3392528142213509</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.2819354703247623</v>
+        <v>0.2896701426666734</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.49880823141631</v>
+        <v>0.4889869467106718</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.3995462405159839</v>
+        <v>0.394837364808361</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.3519124556250235</v>
+        <v>0.3552465402686676</v>
       </c>
     </row>
     <row r="23">
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.4996251285875951</v>
+        <v>0.4912254032521671</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.4106805262273104</v>
+        <v>0.4068366658119761</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.3527606620784921</v>
+        <v>0.3588727287621079</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.4183969623217635</v>
+        <v>0.4193201577281759</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.3112787372634779</v>
+        <v>0.3070953334356151</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.2301624121584185</v>
+        <v>0.2458290466998841</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.4737892057387402</v>
+        <v>0.4650060060091347</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.374054728858</v>
+        <v>0.368577974390697</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.3163417680633482</v>
+        <v>0.3209409335061819</v>
       </c>
     </row>
     <row r="24">
@@ -1356,31 +1356,31 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.5780499329764833</v>
+        <v>0.5605990219570122</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.4857564590195868</v>
+        <v>0.4770889245991267</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.4609695998547796</v>
+        <v>0.4607130629950928</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.4961899191565701</v>
+        <v>0.4863457808887923</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.3837152213913932</v>
+        <v>0.3737586846368712</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.3296438253972433</v>
+        <v>0.3411294923580518</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.526522940532226</v>
+        <v>0.5113904973995648</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.4236813438132241</v>
+        <v>0.4182105055239382</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.3939399839100733</v>
+        <v>0.3937233960810387</v>
       </c>
     </row>
     <row r="25">
@@ -1433,7 +1433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>17</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -1568,31 +1568,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>28461</v>
+        <v>32724</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>30054</v>
+        <v>34243</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13090</v>
+        <v>14553</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>31300</v>
+        <v>34947</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18743</v>
+        <v>22344</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>12069</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>59760</v>
+        <v>67671</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>48797</v>
+        <v>56586</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>25159</v>
+        <v>26622</v>
       </c>
     </row>
     <row r="6">
@@ -1603,31 +1603,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>22077</v>
+        <v>26007</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>23502</v>
+        <v>27016</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7736</v>
+        <v>9105</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>24872</v>
+        <v>27553</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>13050</v>
+        <v>17271</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>7734</v>
+        <v>7449</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>50229</v>
+        <v>56974</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>40660</v>
+        <v>47492</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>18514</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="7">
@@ -1638,31 +1638,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>34417</v>
+        <v>39663</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>36097</v>
+        <v>41199</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>18943</v>
+        <v>21073</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>38493</v>
+        <v>41957</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>25244</v>
+        <v>29152</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18205</v>
+        <v>17727</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>68574</v>
+        <v>77493</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>57578</v>
+        <v>65965</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>32966</v>
+        <v>34204</v>
       </c>
     </row>
     <row r="8">
@@ -1677,28 +1677,28 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>39</v>
@@ -1712,31 +1712,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>38393</v>
+        <v>44906</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>30585</v>
+        <v>36381</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>17853</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>28624</v>
+        <v>30120</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>14270</v>
+        <v>16922</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>9047</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>67017</v>
+        <v>75025</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>44855</v>
+        <v>53303</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>26900</v>
+        <v>26899</v>
       </c>
     </row>
     <row r="10">
@@ -1747,31 +1747,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>31199</v>
+        <v>37758</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>23957</v>
+        <v>28924</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>11975</v>
+        <v>11989</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>22205</v>
+        <v>23160</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9818</v>
+        <v>12140</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>5354</v>
+        <v>5357</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>57802</v>
+        <v>64410</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>36175</v>
+        <v>43820</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>20177</v>
+        <v>20174</v>
       </c>
     </row>
     <row r="11">
@@ -1782,31 +1782,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>44422</v>
+        <v>52497</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>37826</v>
+        <v>43654</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>23419</v>
+        <v>23826</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>35624</v>
+        <v>37304</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>21265</v>
+        <v>23403</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>13860</v>
+        <v>14212</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>77455</v>
+        <v>84641</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>53530</v>
+        <v>63515</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>34728</v>
+        <v>35299</v>
       </c>
     </row>
     <row r="12">
@@ -1821,31 +1821,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -1856,31 +1856,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36156</v>
+        <v>38873</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>26607</v>
+        <v>31211</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>12834</v>
+        <v>12835</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>22205</v>
+        <v>26166</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>14138</v>
+        <v>16017</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3927</v>
+        <v>4802</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>58360</v>
+        <v>65039</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>40745</v>
+        <v>47228</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>16762</v>
+        <v>17637</v>
       </c>
     </row>
     <row r="14">
@@ -1891,31 +1891,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>29985</v>
+        <v>32228</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>20514</v>
+        <v>24683</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8649</v>
+        <v>8588</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>16430</v>
+        <v>19423</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9565</v>
+        <v>11165</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1658</v>
+        <v>2248</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>48586</v>
+        <v>55806</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>32718</v>
+        <v>39543</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>11879</v>
+        <v>12567</v>
       </c>
     </row>
     <row r="15">
@@ -1926,31 +1926,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>42453</v>
+        <v>45467</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33181</v>
+        <v>37085</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>17291</v>
+        <v>17815</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>28678</v>
+        <v>32743</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>20866</v>
+        <v>21748</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7700</v>
+        <v>8521</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>66433</v>
+        <v>75156</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>48735</v>
+        <v>55419</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>23218</v>
+        <v>23931</v>
       </c>
     </row>
     <row r="16">
@@ -1965,31 +1965,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -2000,31 +2000,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>86819</v>
+        <v>99702</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>64320</v>
+        <v>84136</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>34512</v>
+        <v>36775</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>61694</v>
+        <v>72946</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>60341</v>
+        <v>68705</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>21123</v>
+        <v>21948</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>148514</v>
+        <v>172649</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>124661</v>
+        <v>152841</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>55635</v>
+        <v>58723</v>
       </c>
     </row>
     <row r="18">
@@ -2035,31 +2035,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>75516</v>
+        <v>88078</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>54796</v>
+        <v>73568</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>26165</v>
+        <v>27653</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>52044</v>
+        <v>63035</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>50523</v>
+        <v>58121</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>15301</v>
+        <v>15920</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>134576</v>
+        <v>158112</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>110936</v>
+        <v>136707</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>44659</v>
+        <v>48719</v>
       </c>
     </row>
     <row r="19">
@@ -2070,31 +2070,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>96065</v>
+        <v>111429</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>74281</v>
+        <v>94927</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>44450</v>
+        <v>46217</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>71118</v>
+        <v>83012</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>70684</v>
+        <v>79214</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>27853</v>
+        <v>29159</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>163946</v>
+        <v>188808</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>138748</v>
+        <v>169543</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>67226</v>
+        <v>72048</v>
       </c>
     </row>
     <row r="20">
@@ -2109,31 +2109,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D20" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="G20" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>52</v>
-      </c>
       <c r="H20" s="6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -2144,31 +2144,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>48443</v>
+        <v>59576</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>48167</v>
+        <v>54150</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>24826</v>
+        <v>27046</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>54416</v>
+        <v>67559</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>35026</v>
+        <v>43881</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>15908</v>
+        <v>19608</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>102859</v>
+        <v>127134</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>83193</v>
+        <v>98031</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>40735</v>
+        <v>46654</v>
       </c>
     </row>
     <row r="22">
@@ -2179,31 +2179,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>39910</v>
+        <v>50737</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>39704</v>
+        <v>45153</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>19181</v>
+        <v>20478</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>46215</v>
+        <v>57933</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>27615</v>
+        <v>35173</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>11645</v>
+        <v>14331</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>90444</v>
+        <v>113620</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>71411</v>
+        <v>85089</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>33119</v>
+        <v>38174</v>
       </c>
     </row>
     <row r="23">
@@ -2214,31 +2214,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>56002</v>
+        <v>69553</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>57079</v>
+        <v>63768</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>30935</v>
+        <v>34040</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>62518</v>
+        <v>77101</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>43567</v>
+        <v>53057</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>20775</v>
+        <v>24357</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>114791</v>
+        <v>139453</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>94328</v>
+        <v>111338</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>48728</v>
+        <v>54993</v>
       </c>
     </row>
     <row r="24">
@@ -2253,28 +2253,28 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>22</v>
@@ -2288,28 +2288,28 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>29305</v>
+        <v>33566</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>24577</v>
+        <v>28097</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>15194</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>20876</v>
+        <v>24104</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>17233</v>
+        <v>17868</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>3605</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>50181</v>
+        <v>57670</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>41810</v>
+        <v>45966</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>18799</v>
@@ -2323,28 +2323,28 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>23459</v>
+        <v>26723</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>18422</v>
+        <v>22082</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>9965</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>15419</v>
+        <v>18159</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>12099</v>
+        <v>12974</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>1473</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>42101</v>
+        <v>49795</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>34727</v>
+        <v>37447</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>12786</v>
@@ -2358,28 +2358,28 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>35227</v>
+        <v>39893</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>30918</v>
+        <v>34452</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20854</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>26102</v>
+        <v>29674</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>22860</v>
+        <v>23836</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>8309</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>58660</v>
+        <v>66218</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>50211</v>
+        <v>54741</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>26299</v>
@@ -2397,31 +2397,31 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>698</v>
+        <v>807</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>558</v>
+        <v>661</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
@@ -2432,31 +2432,31 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>267577</v>
+        <v>309347</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>224310</v>
+        <v>268218</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>118309</v>
+        <v>124255</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>219114</v>
+        <v>255842</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>159750</v>
+        <v>185737</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>65679</v>
+        <v>71080</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>486691</v>
+        <v>565189</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>384060</v>
+        <v>453955</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>183988</v>
+        <v>195334</v>
       </c>
     </row>
     <row r="30">
@@ -2467,31 +2467,31 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>247548</v>
+        <v>290381</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>205594</v>
+        <v>245012</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>102253</v>
+        <v>109267</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>200931</v>
+        <v>236791</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>143382</v>
+        <v>168131</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>53618</v>
+        <v>60322</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>462280</v>
+        <v>537471</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>359557</v>
+        <v>423764</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>165391</v>
+        <v>176471</v>
       </c>
     </row>
     <row r="31">
@@ -2502,31 +2502,31 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>286405</v>
+        <v>331390</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>243178</v>
+        <v>287321</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>133619</v>
+        <v>140275</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>238290</v>
+        <v>274640</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>176748</v>
+        <v>204629</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>76793</v>
+        <v>83707</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>513733</v>
+        <v>591084</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>407260</v>
+        <v>480828</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>205961</v>
+        <v>216491</v>
       </c>
     </row>
     <row r="32">
